--- a/data/trans_camb/IP24_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP24_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 7,09</t>
+          <t>-12,04; 7,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 7,64</t>
+          <t>-13,43; 5,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,25; -1,81</t>
+          <t>-19,52; -2,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,7; 0,68</t>
+          <t>-17,8; 0,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 9,55</t>
+          <t>-10,86; 8,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,65; 1,37</t>
+          <t>-16,98; 1,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 1,92</t>
+          <t>-12,26; 1,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 5,37</t>
+          <t>-8,69; 5,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,93; -2,36</t>
+          <t>-15,18; -2,2</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-42,09; 39,74</t>
+          <t>-43,44; 39,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-46,08; 41,11</t>
+          <t>-49,28; 30,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-67,04; -7,59</t>
+          <t>-67,1; -9,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-59,05; 4,41</t>
+          <t>-59,45; 5,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,5; 46,73</t>
+          <t>-35,85; 44,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-55,71; 6,75</t>
+          <t>-56,12; 8,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-44,08; 9,68</t>
+          <t>-44,27; 9,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,33; 25,95</t>
+          <t>-31,24; 25,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-54,96; -10,55</t>
+          <t>-55,07; -10,08</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,39; 1,61</t>
+          <t>-18,27; 0,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 7,2</t>
+          <t>-12,39; 7,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,94; 5,61</t>
+          <t>-14,35; 4,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,2; 5,08</t>
+          <t>-12,83; 5,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 6,43</t>
+          <t>-12,25; 4,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 1,0</t>
+          <t>-16,65; 1,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 0,4</t>
+          <t>-13,4; 0,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 4,03</t>
+          <t>-9,3; 3,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 0,42</t>
+          <t>-12,41; 0,94</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-62,15; 11,39</t>
+          <t>-61,7; 4,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-41,73; 38,51</t>
+          <t>-41,7; 40,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-48,61; 31,26</t>
+          <t>-51,67; 27,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-55,8; 32,94</t>
+          <t>-51,95; 38,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-47,37; 48,52</t>
+          <t>-48,06; 33,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-64,42; 10,22</t>
+          <t>-66,71; 10,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,79; 2,38</t>
+          <t>-51,31; 1,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,47; 22,5</t>
+          <t>-36,33; 22,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-51,45; 2,4</t>
+          <t>-48,83; 4,87</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 10,74</t>
+          <t>-12,46; 10,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 12,84</t>
+          <t>-10,8; 12,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,7; 5,9</t>
+          <t>-17,85; 5,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 4,7</t>
+          <t>-13,39; 5,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,16; 2,23</t>
+          <t>-15,76; 3,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,11; 7,37</t>
+          <t>-15,08; 6,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 5,23</t>
+          <t>-8,7; 5,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 5,09</t>
+          <t>-10,42; 4,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 2,28</t>
+          <t>-13,55; 3,45</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,09; 62,52</t>
+          <t>-42,96; 61,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-41,12; 75,58</t>
+          <t>-37,95; 68,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-64,14; 37,95</t>
+          <t>-64,83; 32,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,55; 28,51</t>
+          <t>-54,2; 30,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-63,05; 15,99</t>
+          <t>-62,87; 23,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,68; 45,84</t>
+          <t>-64,64; 46,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-36,29; 30,29</t>
+          <t>-35,34; 33,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-39,61; 30,53</t>
+          <t>-43,64; 26,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-56,15; 14,3</t>
+          <t>-55,99; 19,67</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,26; 2,57</t>
+          <t>-11,02; 2,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 3,11</t>
+          <t>-10,98; 2,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 32,57</t>
+          <t>-0,45; 37,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,37; -0,5</t>
+          <t>-12,43; -0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,8; -2,11</t>
+          <t>-13,78; -0,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 4,24</t>
+          <t>-9,2; 4,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,18; -0,56</t>
+          <t>-9,66; 0,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,64; -1,95</t>
+          <t>-10,4; -1,44</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 19,38</t>
+          <t>-2,33; 19,04</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-38,66; 12,38</t>
+          <t>-38,12; 11,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-37,55; 15,38</t>
+          <t>-37,07; 12,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 148,02</t>
+          <t>-1,88; 156,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-48,87; -2,36</t>
+          <t>-48,62; 0,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-56,58; -9,41</t>
+          <t>-53,41; -4,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-36,21; 21,7</t>
+          <t>-35,33; 24,22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-38,59; -2,98</t>
+          <t>-36,86; 1,31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-40,57; -8,32</t>
+          <t>-39,89; -5,93</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 89,96</t>
+          <t>-9,65; 85,95</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-20,89; -2,17</t>
+          <t>-21,09; -2,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-22,62; -4,28</t>
+          <t>-21,48; -3,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-25,24; -7,84</t>
+          <t>-25,46; -8,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 2,55</t>
+          <t>-13,36; 2,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-14,97; 0,56</t>
+          <t>-15,14; 0,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 17,36</t>
+          <t>-8,6; 18,52</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-14,15; -2,12</t>
+          <t>-14,09; -1,56</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-14,85; -2,98</t>
+          <t>-15,31; -3,76</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-13,02; 4,1</t>
+          <t>-13,86; 3,56</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-54,41; -6,76</t>
+          <t>-55,49; -9,43</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-58,16; -13,71</t>
+          <t>-57,38; -13,64</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-68,34; -27,67</t>
+          <t>-69,05; -29,04</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-51,88; 15,54</t>
+          <t>-53,08; 14,53</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-56,9; 4,32</t>
+          <t>-57,01; 2,67</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-38,91; 110,22</t>
+          <t>-38,0; 104,66</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-47,29; -7,99</t>
+          <t>-48,69; -7,01</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-49,92; -12,25</t>
+          <t>-51,05; -16,46</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-46,64; 18,69</t>
+          <t>-48,08; 18,4</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 11,77</t>
+          <t>-11,94; 11,57</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,58; 25,93</t>
+          <t>0,63; 25,27</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-12,75; 9,47</t>
+          <t>-13,92; 9,33</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-26,19; -3,67</t>
+          <t>-24,56; -2,63</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-23,53; -0,68</t>
+          <t>-22,18; -0,62</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-28,47; -5,92</t>
+          <t>-27,99; -7,24</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-16,52; -0,72</t>
+          <t>-15,5; 0,47</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 8,87</t>
+          <t>-8,06; 9,65</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-16,93; -2,0</t>
+          <t>-17,22; -1,75</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-44,48; 75,33</t>
+          <t>-47,7; 70,35</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5,21; 166,73</t>
+          <t>-0,26; 150,84</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-50,22; 64,0</t>
+          <t>-54,35; 59,55</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-72,36; -14,7</t>
+          <t>-69,75; -9,36</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-65,8; 1,02</t>
+          <t>-64,49; -1,58</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-77,3; -19,02</t>
+          <t>-78,33; -27,04</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-54,3; -1,81</t>
+          <t>-53,89; 2,12</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-26,99; 40,72</t>
+          <t>-28,31; 45,2</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-58,76; -8,86</t>
+          <t>-58,85; -5,83</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,52; -1,04</t>
+          <t>-8,52; -0,86</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 0,61</t>
+          <t>-6,66; 0,47</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 10,0</t>
+          <t>-7,39; 7,75</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-10,07; -3,18</t>
+          <t>-10,15; -3,28</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-9,81; -3,16</t>
+          <t>-9,92; -3,25</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 0,47</t>
+          <t>-8,83; -0,06</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-8,26; -3,32</t>
+          <t>-8,4; -3,36</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,14; -2,13</t>
+          <t>-7,25; -2,19</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 1,65</t>
+          <t>-6,73; 2,43</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-30,92; -3,97</t>
+          <t>-30,87; -3,34</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-25,02; 2,75</t>
+          <t>-24,14; 2,15</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-27,19; 42,55</t>
+          <t>-27,7; 31,29</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-41,3; -15,2</t>
+          <t>-41,23; -15,56</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-39,38; -14,42</t>
+          <t>-39,54; -14,9</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-35,79; 2,66</t>
+          <t>-35,76; 0,39</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-32,82; -14,45</t>
+          <t>-32,92; -14,99</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-28,11; -9,43</t>
+          <t>-28,14; -9,51</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-27,51; 7,83</t>
+          <t>-26,93; 10,24</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP24_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP24_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 7,67</t>
+          <t>-11,64; 7,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 5,68</t>
+          <t>-13,53; 6,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,52; -2,04</t>
+          <t>-19,69; -1,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,8; 0,96</t>
+          <t>-17,44; 2,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 8,94</t>
+          <t>-10,43; 8,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 1,58</t>
+          <t>-17,45; 2,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 1,71</t>
+          <t>-12,23; 1,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 5,36</t>
+          <t>-8,43; 5,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-15,18; -2,2</t>
+          <t>-15,05; -2,27</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-43,44; 39,83</t>
+          <t>-42,45; 38,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-49,28; 30,82</t>
+          <t>-50,09; 37,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-67,1; -9,04</t>
+          <t>-68,05; -8,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-59,45; 5,78</t>
+          <t>-57,59; 14,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-35,85; 44,15</t>
+          <t>-35,46; 40,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-56,12; 8,9</t>
+          <t>-56,37; 11,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-44,27; 9,31</t>
+          <t>-44,01; 5,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,24; 25,44</t>
+          <t>-31,03; 25,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-55,07; -10,08</t>
+          <t>-55,25; -10,29</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-18,27; 0,77</t>
+          <t>-18,33; 1,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 7,32</t>
+          <t>-12,03; 7,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,35; 4,9</t>
+          <t>-15,49; 5,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 5,42</t>
+          <t>-12,44; 5,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 4,86</t>
+          <t>-13,18; 5,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,65; 1,15</t>
+          <t>-16,25; 1,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 0,39</t>
+          <t>-13,58; -0,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 3,94</t>
+          <t>-9,82; 3,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 0,94</t>
+          <t>-12,9; 0,54</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-61,7; 4,34</t>
+          <t>-61,02; 9,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-41,7; 40,25</t>
+          <t>-40,92; 43,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-51,67; 27,66</t>
+          <t>-52,6; 31,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-51,95; 38,54</t>
+          <t>-51,5; 35,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-48,06; 33,73</t>
+          <t>-50,55; 32,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,71; 10,99</t>
+          <t>-65,93; 11,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-51,31; 1,64</t>
+          <t>-50,62; 1,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,33; 22,87</t>
+          <t>-38,89; 19,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-48,83; 4,87</t>
+          <t>-51,45; 3,21</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 10,74</t>
+          <t>-10,99; 11,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 12,2</t>
+          <t>-11,82; 12,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,85; 5,05</t>
+          <t>-17,28; 7,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,39; 5,01</t>
+          <t>-13,29; 5,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,76; 3,34</t>
+          <t>-14,86; 3,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,08; 6,58</t>
+          <t>-14,67; 7,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 5,81</t>
+          <t>-8,69; 5,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 4,42</t>
+          <t>-10,35; 4,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 3,45</t>
+          <t>-13,69; 2,92</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-42,96; 61,89</t>
+          <t>-38,43; 65,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-37,95; 68,95</t>
+          <t>-41,6; 71,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-64,83; 32,02</t>
+          <t>-62,73; 46,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,2; 30,23</t>
+          <t>-54,62; 35,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-62,87; 23,27</t>
+          <t>-61,78; 17,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,64; 46,48</t>
+          <t>-63,14; 44,85</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-35,34; 33,8</t>
+          <t>-34,98; 35,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-43,64; 26,24</t>
+          <t>-42,63; 23,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-55,99; 19,67</t>
+          <t>-55,54; 20,11</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,02; 2,29</t>
+          <t>-11,02; 2,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 2,57</t>
+          <t>-10,59; 2,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 37,13</t>
+          <t>-0,08; 37,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,43; -0,0</t>
+          <t>-12,55; -0,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,78; -0,96</t>
+          <t>-14,48; -2,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 4,84</t>
+          <t>-9,08; 4,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 0,13</t>
+          <t>-9,84; -0,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,4; -1,44</t>
+          <t>-10,53; -1,77</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 19,04</t>
+          <t>-2,2; 20,32</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-38,12; 11,03</t>
+          <t>-38,63; 14,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-37,07; 12,33</t>
+          <t>-36,78; 10,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 156,14</t>
+          <t>-0,48; 169,02</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-48,62; 0,02</t>
+          <t>-49,68; -1,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-53,41; -4,85</t>
+          <t>-56,09; -11,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-35,33; 24,22</t>
+          <t>-35,94; 22,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-36,86; 1,31</t>
+          <t>-37,42; -3,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-39,89; -5,93</t>
+          <t>-39,71; -8,04</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 85,95</t>
+          <t>-9,33; 92,31</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-21,09; -2,71</t>
+          <t>-20,92; -2,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-21,48; -3,72</t>
+          <t>-22,24; -3,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-25,46; -8,2</t>
+          <t>-25,23; -6,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-13,36; 2,48</t>
+          <t>-13,2; 2,41</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-15,14; 0,28</t>
+          <t>-15,05; 0,39</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 18,52</t>
+          <t>-9,12; 17,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-14,09; -1,56</t>
+          <t>-14,29; -2,5</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-15,31; -3,76</t>
+          <t>-15,05; -3,65</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 3,56</t>
+          <t>-13,88; 3,19</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-55,49; -9,43</t>
+          <t>-55,44; -8,54</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-57,38; -13,64</t>
+          <t>-58,22; -14,39</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-69,05; -29,04</t>
+          <t>-67,64; -24,51</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-53,08; 14,53</t>
+          <t>-51,94; 14,84</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-57,01; 2,67</t>
+          <t>-57,09; 3,4</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-38,0; 104,66</t>
+          <t>-38,8; 101,26</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-48,69; -7,01</t>
+          <t>-47,48; -11,08</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-51,05; -16,46</t>
+          <t>-51,29; -14,27</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-48,08; 18,4</t>
+          <t>-47,12; 17,88</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 11,57</t>
+          <t>-12,59; 10,36</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,63; 25,27</t>
+          <t>0,79; 26,1</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 9,33</t>
+          <t>-13,1; 10,04</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-24,56; -2,63</t>
+          <t>-26,16; -3,96</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-22,18; -0,62</t>
+          <t>-23,81; -1,26</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-27,99; -7,24</t>
+          <t>-27,91; -5,87</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 0,47</t>
+          <t>-16,1; 0,76</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 9,65</t>
+          <t>-7,96; 9,8</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-17,22; -1,75</t>
+          <t>-18,21; -1,61</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-47,7; 70,35</t>
+          <t>-49,21; 64,3</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 150,84</t>
+          <t>2,58; 164,53</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-54,35; 59,55</t>
+          <t>-52,28; 64,43</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-69,75; -9,36</t>
+          <t>-70,3; -15,19</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-64,49; -1,58</t>
+          <t>-67,12; -3,75</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-78,33; -27,04</t>
+          <t>-77,3; -19,47</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-53,89; 2,12</t>
+          <t>-54,62; 3,75</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-28,31; 45,2</t>
+          <t>-26,85; 47,03</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-58,85; -5,83</t>
+          <t>-60,68; -5,93</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,52; -0,86</t>
+          <t>-8,92; -1,22</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 0,47</t>
+          <t>-7,16; 0,53</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 7,75</t>
+          <t>-6,71; 8,32</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-10,15; -3,28</t>
+          <t>-10,27; -3,52</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-9,92; -3,25</t>
+          <t>-9,92; -3,02</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-8,83; -0,06</t>
+          <t>-9,13; 0,03</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-8,4; -3,36</t>
+          <t>-8,33; -3,18</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,25; -2,19</t>
+          <t>-7,29; -1,95</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 2,43</t>
+          <t>-6,81; 2,42</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-30,87; -3,34</t>
+          <t>-32,04; -4,99</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-24,14; 2,15</t>
+          <t>-26,43; 2,43</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-27,7; 31,29</t>
+          <t>-26,09; 35,21</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-41,23; -15,56</t>
+          <t>-41,58; -16,09</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-39,54; -14,9</t>
+          <t>-39,34; -13,47</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-35,76; 0,39</t>
+          <t>-36,47; 0,67</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-32,92; -14,99</t>
+          <t>-32,67; -13,75</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-28,14; -9,51</t>
+          <t>-28,86; -8,79</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-26,93; 10,24</t>
+          <t>-27,62; 11,31</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP24_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP24_R-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-8,2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,21</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-7,64</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-2,54</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-3,26</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-10,32</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-8,2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,21</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-7,61</t>
+          <t>-10,9</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-8,63</t>
+          <t>-9,02</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 7,42</t>
+          <t>-17,7; 0,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 6,83</t>
+          <t>-10,36; 9,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,69; -1,99</t>
+          <t>-16,57; 1,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,44; 2,65</t>
+          <t>-11,94; 7,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 8,63</t>
+          <t>-12,72; 7,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,45; 2,49</t>
+          <t>-19,64; -2,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,23; 1,03</t>
+          <t>-12,3; 1,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 5,3</t>
+          <t>-8,59; 5,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-15,05; -2,27</t>
+          <t>-15,29; -2,91</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-32,58%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-0,85%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-30,35%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-10,91%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-13,98%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-44,25%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-32,58%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-0,85%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-30,25%</t>
+          <t>-46,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-35,65%</t>
+          <t>-37,25%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-42,45; 38,99</t>
+          <t>-59,05; 4,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-50,09; 37,05</t>
+          <t>-33,5; 46,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-68,05; -8,07</t>
+          <t>-56,67; 7,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-57,59; 14,37</t>
+          <t>-42,09; 39,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-35,46; 40,88</t>
+          <t>-46,08; 41,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-56,37; 11,2</t>
+          <t>-68,71; -12,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-44,01; 5,25</t>
+          <t>-44,08; 9,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,03; 25,15</t>
+          <t>-31,33; 25,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-55,25; -10,29</t>
+          <t>-56,33; -13,78</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-3,84</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-3,52</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-8,23</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-8,35</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-2,35</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-4,68</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-3,84</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-3,52</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-7,67</t>
+          <t>-5,16</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-6,21</t>
+          <t>-6,62</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-18,33; 1,23</t>
+          <t>-14,2; 5,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 7,99</t>
+          <t>-11,7; 6,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,49; 5,38</t>
+          <t>-16,28; 0,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,44; 5,44</t>
+          <t>-17,39; 1,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 5,14</t>
+          <t>-12,35; 7,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,25; 1,5</t>
+          <t>-14,67; 4,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-13,58; -0,21</t>
+          <t>-12,93; 0,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 3,38</t>
+          <t>-9,27; 4,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 0,54</t>
+          <t>-13,58; -0,02</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-18,98%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-17,4%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-40,62%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-34,98%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-9,84%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-19,6%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-18,98%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-17,4%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-37,88%</t>
+          <t>-21,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-28,11%</t>
+          <t>-29,96%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-61,02; 9,56</t>
+          <t>-55,8; 32,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-40,92; 43,5</t>
+          <t>-47,37; 48,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-52,6; 31,69</t>
+          <t>-66,32; 8,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-51,5; 35,67</t>
+          <t>-62,15; 11,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,55; 32,92</t>
+          <t>-41,73; 38,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-65,93; 11,29</t>
+          <t>-50,52; 27,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-50,62; 1,95</t>
+          <t>-49,79; 2,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,89; 19,29</t>
+          <t>-36,47; 22,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-51,45; 3,21</t>
+          <t>-52,55; 1,39</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-3,97</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-6,17</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-9,24</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-0,31</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,51</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-6,97</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-3,97</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-6,17</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-5,63</t>
+          <t>-8,24</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-6,09</t>
+          <t>-8,5</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 11,08</t>
+          <t>-13,37; 4,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 12,46</t>
+          <t>-16,16; 2,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,28; 7,5</t>
+          <t>-17,57; -0,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,29; 5,68</t>
+          <t>-11,27; 10,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,86; 3,03</t>
+          <t>-11,84; 12,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,67; 7,26</t>
+          <t>-19,02; 4,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 5,96</t>
+          <t>-9,04; 5,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 4,16</t>
+          <t>-9,98; 5,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 2,92</t>
+          <t>-15,49; -1,21</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-19,65%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-30,56%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-45,75%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-1,36%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>2,21%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-30,15%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-19,65%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-30,56%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-27,87%</t>
+          <t>-35,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-28,49%</t>
+          <t>-39,79%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,43; 65,81</t>
+          <t>-54,55; 28,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-41,6; 71,14</t>
+          <t>-63,05; 15,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-62,73; 46,36</t>
+          <t>-72,99; 1,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,62; 35,6</t>
+          <t>-38,09; 62,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-61,78; 17,93</t>
+          <t>-41,12; 75,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-63,14; 44,85</t>
+          <t>-67,22; 27,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-34,98; 35,53</t>
+          <t>-36,29; 30,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-42,63; 23,4</t>
+          <t>-39,61; 30,53</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-55,54; 20,11</t>
+          <t>-61,53; -5,15</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-6,4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-8,28</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-3,67</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-4,08</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-4,31</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>11,97</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-6,4</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-8,28</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,43</t>
+          <t>-1,23</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,79</t>
+          <t>-2,6</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,02; 2,8</t>
+          <t>-12,37; -0,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 2,24</t>
+          <t>-14,8; -2,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 37,11</t>
+          <t>-10,24; 2,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,55; -0,25</t>
+          <t>-11,26; 2,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,48; -2,18</t>
+          <t>-11,01; 3,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 4,58</t>
+          <t>-8,64; 5,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-9,84; -0,75</t>
+          <t>-10,18; -0,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,53; -1,77</t>
+          <t>-10,64; -1,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 20,32</t>
+          <t>-7,41; 2,4</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-28,09%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-36,31%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-16,09%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-15,98%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-16,88%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>46,9%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-28,09%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-36,31%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-10,68%</t>
+          <t>-4,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>-10,75%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-38,63; 14,04</t>
+          <t>-48,87; -2,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,78; 10,46</t>
+          <t>-56,58; -9,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 169,02</t>
+          <t>-39,76; 15,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-49,68; -1,55</t>
+          <t>-38,66; 12,38</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-56,09; -11,01</t>
+          <t>-37,55; 15,38</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-35,94; 22,38</t>
+          <t>-29,94; 26,84</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-37,42; -3,29</t>
+          <t>-38,59; -2,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-39,71; -8,04</t>
+          <t>-40,57; -8,32</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 92,31</t>
+          <t>-27,85; 11,13</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-5,63</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-6,66</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-1,71</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-11,74</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-12,69</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-16,19</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-5,63</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-6,66</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>-17,51</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-6,84</t>
+          <t>-8,81</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-20,92; -2,81</t>
+          <t>-13,37; 2,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-22,24; -3,86</t>
+          <t>-14,97; 0,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-25,23; -6,95</t>
+          <t>-10,75; 14,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 2,41</t>
+          <t>-20,89; -2,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 0,39</t>
+          <t>-22,62; -4,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 17,54</t>
+          <t>-26,81; -9,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-14,29; -2,5</t>
+          <t>-14,15; -2,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-15,05; -3,65</t>
+          <t>-14,85; -2,98</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-13,88; 3,19</t>
+          <t>-14,69; 1,13</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-26,15%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-30,93%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-7,93%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-36,33%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-39,27%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-50,13%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-26,15%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-30,93%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>-54,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-25,93%</t>
+          <t>-33,38%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-55,44; -8,54</t>
+          <t>-51,88; 15,54</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-58,22; -14,39</t>
+          <t>-56,9; 4,32</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-67,64; -24,51</t>
+          <t>-44,67; 88,76</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-51,94; 14,84</t>
+          <t>-54,41; -6,76</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-57,09; 3,4</t>
+          <t>-58,16; -13,71</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-38,8; 101,26</t>
+          <t>-71,25; -33,9</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-47,48; -11,08</t>
+          <t>-47,29; -7,99</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-51,29; -14,27</t>
+          <t>-49,92; -12,25</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-47,12; 17,88</t>
+          <t>-51,85; 6,3</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-14,83</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-12,44</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-18,24</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-0,52</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>13,74</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-2,47</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-14,83</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-12,44</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-17,34</t>
+          <t>-5,67</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-9,9</t>
+          <t>-11,87</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 10,36</t>
+          <t>-26,19; -3,67</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,79; 26,1</t>
+          <t>-23,53; -0,68</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 10,04</t>
+          <t>-29,49; -7,24</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-26,16; -3,96</t>
+          <t>-11,08; 11,77</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-23,81; -1,26</t>
+          <t>1,58; 25,93</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-27,91; -5,87</t>
+          <t>-15,1; 5,54</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-16,1; 0,76</t>
+          <t>-16,52; -0,72</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 9,8</t>
+          <t>-7,79; 8,87</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-18,21; -1,61</t>
+          <t>-18,98; -4,44</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-48,69%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-40,84%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-59,89%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-2,49%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>65,8%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-11,81%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-48,69%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-40,84%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-56,93%</t>
+          <t>-27,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-38,67%</t>
+          <t>-46,36%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-49,21; 64,3</t>
+          <t>-72,36; -14,7</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2,58; 164,53</t>
+          <t>-65,8; 1,02</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-52,28; 64,43</t>
+          <t>-79,55; -25,24</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-70,3; -15,19</t>
+          <t>-44,48; 75,33</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-67,12; -3,75</t>
+          <t>5,21; 166,73</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-77,3; -19,47</t>
+          <t>-60,11; 39,23</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-54,62; 3,75</t>
+          <t>-54,3; -1,81</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-26,85; 47,03</t>
+          <t>-26,99; 40,72</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-60,68; -5,93</t>
+          <t>-64,75; -20,04</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-6,74</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-6,32</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-6,32</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-4,82</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-3,01</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-1,87</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-6,74</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-6,32</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-4,97</t>
+          <t>-7,46</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-3,55</t>
+          <t>-6,88</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,92; -1,22</t>
+          <t>-10,07; -3,18</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 0,53</t>
+          <t>-9,81; -3,16</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 8,32</t>
+          <t>-9,93; -1,26</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-10,27; -3,52</t>
+          <t>-8,52; -1,04</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-9,92; -3,02</t>
+          <t>-6,89; 0,61</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 0,03</t>
+          <t>-11,14; -3,67</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-8,33; -3,18</t>
+          <t>-8,26; -3,32</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,29; -1,95</t>
+          <t>-7,14; -2,13</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 2,42</t>
+          <t>-9,62; -4,37</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-29,29%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-27,48%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-27,47%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-19,1%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-11,93%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-7,41%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-29,29%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-27,48%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-21,61%</t>
+          <t>-29,54%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-14,75%</t>
+          <t>-28,56%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-32,04; -4,99</t>
+          <t>-41,3; -15,2</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-26,43; 2,43</t>
+          <t>-39,38; -14,42</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-26,09; 35,21</t>
+          <t>-40,12; -5,68</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-41,58; -16,09</t>
+          <t>-30,92; -3,97</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-39,34; -13,47</t>
+          <t>-25,02; 2,75</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-36,47; 0,67</t>
+          <t>-40,96; -15,88</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-32,67; -13,75</t>
+          <t>-32,82; -14,45</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-28,86; -8,79</t>
+          <t>-28,11; -9,43</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-27,62; 11,31</t>
+          <t>-38,48; -18,99</t>
         </is>
       </c>
     </row>
